--- a/docs/seduc.xlsx
+++ b/docs/seduc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\albertreis\projetos\convenios-api\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c83854e6706cf50b/Seplad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C934E410-E746-4DDC-B79C-0CAF6DB14728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="11_422837189A90368121DA598BD8245F1DBCAEB3C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AEF0A85-DAA4-4BCF-A1B8-677A55AE2965}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lista" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="643">
   <si>
     <t>SEDUC</t>
   </si>
@@ -658,9 +658,6 @@
     <t>CONSTRUÇÃO DE CRECHE PADRÃO SEDUC, LOCALIZADA Á RUA PEDRO VIANA, S/N, SANTA MARIA/PA</t>
   </si>
   <si>
-    <t>24/011/2023</t>
-  </si>
-  <si>
     <t>SÃO MIGUEL DO GUAMÁ</t>
   </si>
   <si>
@@ -860,6 +857,9 @@
   </si>
   <si>
     <t>CONSTRUÇÃO DE CRECHE PADRÃO SEDUC, LOCALIZADA NO BAIRRO PRIMAVERA, TV MOCAJUBA, S/N, CAMETÁ/PA,</t>
+  </si>
+  <si>
+    <t>R$ 6.733.199,77‬</t>
   </si>
   <si>
     <t>034/2023</t>
@@ -2000,8 +2000,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00_);[Red]\(&quot;R$&quot;\ #,###.00\)"/>
     <numFmt numFmtId="165" formatCode="[$R$ -416]#,##0.00"/>
@@ -2111,12 +2110,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2224,34 +2222,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2346,9 +2326,6 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2362,38 +2339,42 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela2" displayName="Tabela2" ref="A1:O146" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela2" displayName="Tabela2" ref="A1:O146" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:O146" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="orgao" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="municipio" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="convenente" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="numero_convenio" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ano" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="orgao" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="municipio" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="convenente" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="numero_convenio" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ano" dataDxfId="11">
       <calculatedColumnFormula>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="plano_interno" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="objeto" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="grupo_despesa" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="data_inicio" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="data_fim" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="valor_total" dataDxfId="4" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="valor_orgao" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="valor_contrapartida" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="quantidade_parcelas" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="aditivo" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="plano_interno" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="objeto" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="grupo_despesa" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="data_inicio" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="data_fim" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="valor_total" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="valor_orgao" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="valor_contrapartida" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="quantidade_parcelas" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="aditivo" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela3" displayName="Tabela3" ref="A1:F582" totalsRowShown="0">
-  <autoFilter ref="A1:F582" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela3" displayName="Tabela3" ref="A1:F588" totalsRowShown="0">
+  <autoFilter ref="A1:F588" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="numero_convenio"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="numero_parcela" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="numero_parcela" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="valor_previsto" dataCellStyle="Vírgula"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="valor_pago" dataCellStyle="Vírgula"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="data_pagamento"/>
@@ -2686,12 +2667,11 @@
     <col min="4" max="4" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="98.5703125" style="5" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="16.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -2729,7 +2709,7 @@
       <c r="J1" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="2" t="s">
         <v>624</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -2777,7 +2757,7 @@
       <c r="J2" s="8">
         <v>46106</v>
       </c>
-      <c r="K2" s="38">
+      <c r="K2" s="9">
         <v>2664650.94</v>
       </c>
       <c r="L2" s="9">
@@ -2825,7 +2805,7 @@
       <c r="J3" s="14">
         <v>46382</v>
       </c>
-      <c r="K3" s="39">
+      <c r="K3" s="15">
         <v>3474467.3</v>
       </c>
       <c r="L3" s="15">
@@ -2873,7 +2853,7 @@
       <c r="J4" s="8">
         <v>46144</v>
       </c>
-      <c r="K4" s="40">
+      <c r="K4" s="20">
         <v>2787550.98</v>
       </c>
       <c r="L4" s="20">
@@ -2921,7 +2901,7 @@
       <c r="J5" s="14">
         <v>46245</v>
       </c>
-      <c r="K5" s="39">
+      <c r="K5" s="15">
         <v>2192548.21</v>
       </c>
       <c r="L5" s="15">
@@ -2969,7 +2949,7 @@
       <c r="J6" s="8">
         <v>46267</v>
       </c>
-      <c r="K6" s="40">
+      <c r="K6" s="20">
         <v>1660745.01</v>
       </c>
       <c r="L6" s="20">
@@ -3017,7 +2997,7 @@
       <c r="J7" s="14">
         <v>46137</v>
       </c>
-      <c r="K7" s="39">
+      <c r="K7" s="15">
         <v>992466.38</v>
       </c>
       <c r="L7" s="15">
@@ -3065,7 +3045,7 @@
       <c r="J8" s="8">
         <v>46152</v>
       </c>
-      <c r="K8" s="40">
+      <c r="K8" s="20">
         <v>7887953.3799999999</v>
       </c>
       <c r="L8" s="20">
@@ -3113,7 +3093,7 @@
       <c r="J9" s="14">
         <v>46101</v>
       </c>
-      <c r="K9" s="39">
+      <c r="K9" s="15">
         <v>2006539.6</v>
       </c>
       <c r="L9" s="15">
@@ -3161,7 +3141,7 @@
       <c r="J10" s="8">
         <v>46101</v>
       </c>
-      <c r="K10" s="40">
+      <c r="K10" s="20">
         <v>1521043.2</v>
       </c>
       <c r="L10" s="20">
@@ -3209,7 +3189,7 @@
       <c r="J11" s="14">
         <v>46147</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="15">
         <v>3194567.83</v>
       </c>
       <c r="L11" s="15">
@@ -3257,7 +3237,7 @@
       <c r="J12" s="8">
         <v>46104</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="20">
         <v>4260742.66</v>
       </c>
       <c r="L12" s="20">
@@ -3305,7 +3285,7 @@
       <c r="J13" s="14">
         <v>46183</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="15">
         <v>5383007.7800000003</v>
       </c>
       <c r="L13" s="15">
@@ -3353,7 +3333,7 @@
       <c r="J14" s="8">
         <v>46372</v>
       </c>
-      <c r="K14" s="40">
+      <c r="K14" s="20">
         <v>11283720.880000001</v>
       </c>
       <c r="L14" s="20">
@@ -3401,7 +3381,7 @@
       <c r="J15" s="14">
         <v>46200</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="15">
         <v>3401677.92</v>
       </c>
       <c r="L15" s="15">
@@ -3449,7 +3429,7 @@
       <c r="J16" s="8">
         <v>46199</v>
       </c>
-      <c r="K16" s="40">
+      <c r="K16" s="20">
         <v>3394138.36</v>
       </c>
       <c r="L16" s="20">
@@ -3497,7 +3477,7 @@
       <c r="J17" s="14">
         <v>46186</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="15">
         <v>1537017.65</v>
       </c>
       <c r="L17" s="15">
@@ -3545,7 +3525,7 @@
       <c r="J18" s="8">
         <v>46390</v>
       </c>
-      <c r="K18" s="40">
+      <c r="K18" s="20">
         <v>4726984.96</v>
       </c>
       <c r="L18" s="20">
@@ -3593,7 +3573,7 @@
       <c r="J19" s="14">
         <v>46201</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="15">
         <v>2451480.7200000002</v>
       </c>
       <c r="L19" s="15">
@@ -3641,7 +3621,7 @@
       <c r="J20" s="8">
         <v>46205</v>
       </c>
-      <c r="K20" s="40">
+      <c r="K20" s="20">
         <v>1913701.8900000001</v>
       </c>
       <c r="L20" s="20">
@@ -3689,7 +3669,7 @@
       <c r="J21" s="14">
         <v>46236</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="15">
         <v>2966391.53</v>
       </c>
       <c r="L21" s="15">
@@ -3737,7 +3717,7 @@
       <c r="J22" s="8">
         <v>46236</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="20">
         <v>2193352.85</v>
       </c>
       <c r="L22" s="20">
@@ -3785,7 +3765,7 @@
       <c r="J23" s="14">
         <v>46205</v>
       </c>
-      <c r="K23" s="39">
+      <c r="K23" s="15">
         <v>5701513.4500000002</v>
       </c>
       <c r="L23" s="15">
@@ -3833,7 +3813,7 @@
       <c r="J24" s="8">
         <v>46267</v>
       </c>
-      <c r="K24" s="40">
+      <c r="K24" s="20">
         <v>7701028.3499999996</v>
       </c>
       <c r="L24" s="20">
@@ -3881,7 +3861,7 @@
       <c r="J25" s="14">
         <v>46179</v>
       </c>
-      <c r="K25" s="39">
+      <c r="K25" s="15">
         <v>4464711.4000000004</v>
       </c>
       <c r="L25" s="15">
@@ -3929,7 +3909,7 @@
       <c r="J26" s="8">
         <v>46389</v>
       </c>
-      <c r="K26" s="40">
+      <c r="K26" s="20">
         <v>4413308.3</v>
       </c>
       <c r="L26" s="20">
@@ -3977,8 +3957,8 @@
       <c r="J27" s="14">
         <v>46207</v>
       </c>
-      <c r="K27" s="39">
-        <v>1176684.72</v>
+      <c r="K27" s="15">
+        <v>4464711.4000000004</v>
       </c>
       <c r="L27" s="15">
         <v>1129617.33</v>
@@ -4025,7 +4005,7 @@
       <c r="J28" s="8">
         <v>46207</v>
       </c>
-      <c r="K28" s="40">
+      <c r="K28" s="20">
         <v>2095890.51</v>
       </c>
       <c r="L28" s="20">
@@ -4073,7 +4053,7 @@
       <c r="J29" s="14">
         <v>46299</v>
       </c>
-      <c r="K29" s="39">
+      <c r="K29" s="15">
         <v>10889479.699999999</v>
       </c>
       <c r="L29" s="15">
@@ -4121,7 +4101,7 @@
       <c r="J30" s="8">
         <v>46082</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="20">
         <v>3394304.27</v>
       </c>
       <c r="L30" s="20">
@@ -4169,7 +4149,7 @@
       <c r="J31" s="14">
         <v>46140</v>
       </c>
-      <c r="K31" s="39">
+      <c r="K31" s="15">
         <v>4902270.55</v>
       </c>
       <c r="L31" s="15">
@@ -4217,7 +4197,7 @@
       <c r="J32" s="8">
         <v>46299</v>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="20">
         <v>5848594.5899999999</v>
       </c>
       <c r="L32" s="20">
@@ -4265,7 +4245,7 @@
       <c r="J33" s="14">
         <v>46201</v>
       </c>
-      <c r="K33" s="39">
+      <c r="K33" s="15">
         <v>2501890.92</v>
       </c>
       <c r="L33" s="15">
@@ -4313,7 +4293,7 @@
       <c r="J34" s="8">
         <v>46201</v>
       </c>
-      <c r="K34" s="40">
+      <c r="K34" s="20">
         <v>5030725.1100000003</v>
       </c>
       <c r="L34" s="20">
@@ -4361,7 +4341,7 @@
       <c r="J35" s="14">
         <v>46199</v>
       </c>
-      <c r="K35" s="39">
+      <c r="K35" s="15">
         <v>2741042.61</v>
       </c>
       <c r="L35" s="15">
@@ -4409,7 +4389,7 @@
       <c r="J36" s="8">
         <v>46299</v>
       </c>
-      <c r="K36" s="40">
+      <c r="K36" s="20">
         <v>1496018.94</v>
       </c>
       <c r="L36" s="20">
@@ -4457,7 +4437,7 @@
       <c r="J37" s="14">
         <v>46094</v>
       </c>
-      <c r="K37" s="39">
+      <c r="K37" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L37" s="15">
@@ -4505,7 +4485,7 @@
       <c r="J38" s="8">
         <v>46094</v>
       </c>
-      <c r="K38" s="40">
+      <c r="K38" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L38" s="20">
@@ -4553,7 +4533,7 @@
       <c r="J39" s="14">
         <v>46078</v>
       </c>
-      <c r="K39" s="39">
+      <c r="K39" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L39" s="15">
@@ -4601,7 +4581,7 @@
       <c r="J40" s="8">
         <v>46094</v>
       </c>
-      <c r="K40" s="40">
+      <c r="K40" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L40" s="20">
@@ -4649,7 +4629,7 @@
       <c r="J41" s="14">
         <v>46078</v>
       </c>
-      <c r="K41" s="39">
+      <c r="K41" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L41" s="15">
@@ -4697,7 +4677,7 @@
       <c r="J42" s="8">
         <v>46138</v>
       </c>
-      <c r="K42" s="40">
+      <c r="K42" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L42" s="20">
@@ -4739,13 +4719,13 @@
       <c r="H43" s="13" t="s">
         <v>629</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>197</v>
+      <c r="I43" s="14">
+        <v>45254</v>
       </c>
       <c r="J43" s="14">
         <v>46078</v>
       </c>
-      <c r="K43" s="39">
+      <c r="K43" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L43" s="15">
@@ -4766,23 +4746,23 @@
         <v>0</v>
       </c>
       <c r="B44" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="D44" s="18" t="s">
         <v>199</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>200</v>
       </c>
       <c r="E44" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F44" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="G44" s="18" t="s">
         <v>201</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>202</v>
       </c>
       <c r="H44" s="19" t="s">
         <v>629</v>
@@ -4793,7 +4773,7 @@
       <c r="J44" s="8">
         <v>46094</v>
       </c>
-      <c r="K44" s="40">
+      <c r="K44" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L44" s="20">
@@ -4814,23 +4794,23 @@
         <v>0</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="D45" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="E45" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F45" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="G45" s="12" t="s">
         <v>206</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>207</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>629</v>
@@ -4841,7 +4821,7 @@
       <c r="J45" s="14">
         <v>46094</v>
       </c>
-      <c r="K45" s="39">
+      <c r="K45" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L45" s="15">
@@ -4862,23 +4842,23 @@
         <v>0</v>
       </c>
       <c r="B46" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="D46" s="18" t="s">
         <v>209</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>210</v>
       </c>
       <c r="E46" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F46" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="18" t="s">
         <v>211</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>212</v>
       </c>
       <c r="H46" s="19" t="s">
         <v>629</v>
@@ -4889,7 +4869,7 @@
       <c r="J46" s="8">
         <v>46094</v>
       </c>
-      <c r="K46" s="40">
+      <c r="K46" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L46" s="20">
@@ -4910,23 +4890,23 @@
         <v>0</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="D47" s="12" t="s">
         <v>214</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>215</v>
       </c>
       <c r="E47" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F47" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="G47" s="12" t="s">
         <v>216</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>217</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>629</v>
@@ -4937,7 +4917,7 @@
       <c r="J47" s="14">
         <v>46186</v>
       </c>
-      <c r="K47" s="39">
+      <c r="K47" s="15">
         <v>6766535.0899999999</v>
       </c>
       <c r="L47" s="15">
@@ -4961,20 +4941,20 @@
         <v>640</v>
       </c>
       <c r="C48" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="18" t="s">
         <v>218</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>219</v>
       </c>
       <c r="E48" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F48" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="G48" s="18" t="s">
         <v>220</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>221</v>
       </c>
       <c r="H48" s="19" t="s">
         <v>629</v>
@@ -4985,7 +4965,7 @@
       <c r="J48" s="8">
         <v>46094</v>
       </c>
-      <c r="K48" s="40">
+      <c r="K48" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L48" s="20">
@@ -5006,23 +4986,23 @@
         <v>0</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="12" t="s">
         <v>223</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>224</v>
       </c>
       <c r="E49" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F49" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="G49" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>226</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>629</v>
@@ -5033,7 +5013,7 @@
       <c r="J49" s="14">
         <v>46078</v>
       </c>
-      <c r="K49" s="39">
+      <c r="K49" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L49" s="15">
@@ -5060,17 +5040,17 @@
         <v>32</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E50" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F50" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="G50" s="18" t="s">
         <v>228</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>229</v>
       </c>
       <c r="H50" s="19" t="s">
         <v>629</v>
@@ -5081,7 +5061,7 @@
       <c r="J50" s="8">
         <v>46186</v>
       </c>
-      <c r="K50" s="40">
+      <c r="K50" s="20">
         <v>6866541.0599999996</v>
       </c>
       <c r="L50" s="20">
@@ -5102,23 +5082,23 @@
         <v>0</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>231</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>232</v>
       </c>
       <c r="E51" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F51" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G51" s="12" t="s">
         <v>233</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>234</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>629</v>
@@ -5129,7 +5109,7 @@
       <c r="J51" s="14">
         <v>46094</v>
       </c>
-      <c r="K51" s="39">
+      <c r="K51" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L51" s="15">
@@ -5150,23 +5130,23 @@
         <v>0</v>
       </c>
       <c r="B52" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="D52" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="E52" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F52" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="G52" s="18" t="s">
         <v>238</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="H52" s="19" t="s">
         <v>629</v>
@@ -5177,7 +5157,7 @@
       <c r="J52" s="8">
         <v>46094</v>
       </c>
-      <c r="K52" s="40">
+      <c r="K52" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L52" s="20">
@@ -5204,17 +5184,17 @@
         <v>144</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E53" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F53" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="G53" s="12" t="s">
         <v>241</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>242</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>629</v>
@@ -5225,7 +5205,7 @@
       <c r="J53" s="14">
         <v>46094</v>
       </c>
-      <c r="K53" s="39">
+      <c r="K53" s="15">
         <v>6866541.0599999996</v>
       </c>
       <c r="L53" s="15">
@@ -5246,23 +5226,23 @@
         <v>0</v>
       </c>
       <c r="B54" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="D54" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="E54" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F54" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="G54" s="18" t="s">
         <v>246</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>247</v>
       </c>
       <c r="H54" s="19" t="s">
         <v>629</v>
@@ -5273,7 +5253,7 @@
       <c r="J54" s="8">
         <v>46101</v>
       </c>
-      <c r="K54" s="40">
+      <c r="K54" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L54" s="20">
@@ -5294,23 +5274,23 @@
         <v>0</v>
       </c>
       <c r="B55" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="D55" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="E55" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F55" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="G55" s="12" t="s">
         <v>251</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>252</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>629</v>
@@ -5321,7 +5301,7 @@
       <c r="J55" s="14">
         <v>46094</v>
       </c>
-      <c r="K55" s="39">
+      <c r="K55" s="15">
         <v>6766535.0899999999</v>
       </c>
       <c r="L55" s="15">
@@ -5342,23 +5322,23 @@
         <v>0</v>
       </c>
       <c r="B56" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="D56" s="18" t="s">
         <v>254</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>255</v>
       </c>
       <c r="E56" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F56" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="G56" s="18" t="s">
         <v>256</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>257</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>629</v>
@@ -5369,7 +5349,7 @@
       <c r="J56" s="8">
         <v>46094</v>
       </c>
-      <c r="K56" s="40">
+      <c r="K56" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L56" s="20">
@@ -5393,20 +5373,20 @@
         <v>77</v>
       </c>
       <c r="C57" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="E57" s="12" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F57" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="G57" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>261</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>629</v>
@@ -5417,7 +5397,7 @@
       <c r="J57" s="14">
         <v>46094</v>
       </c>
-      <c r="K57" s="39">
+      <c r="K57" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L57" s="15">
@@ -5444,17 +5424,17 @@
         <v>63</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E58" s="18" t="str">
         <f>RIGHT(Tabela2[[#This Row],[numero_convenio]],4)</f>
         <v>2023</v>
       </c>
       <c r="F58" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G58" s="18" t="s">
         <v>263</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>264</v>
       </c>
       <c r="H58" s="19" t="s">
         <v>629</v>
@@ -5465,7 +5445,7 @@
       <c r="J58" s="8">
         <v>46094</v>
       </c>
-      <c r="K58" s="40">
+      <c r="K58" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L58" s="20">
@@ -5513,7 +5493,7 @@
       <c r="J59" s="14">
         <v>46137</v>
       </c>
-      <c r="K59" s="39">
+      <c r="K59" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L59" s="15">
@@ -5561,7 +5541,7 @@
       <c r="J60" s="8">
         <v>46094</v>
       </c>
-      <c r="K60" s="40">
+      <c r="K60" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L60" s="20">
@@ -5609,7 +5589,7 @@
       <c r="J61" s="14">
         <v>46089</v>
       </c>
-      <c r="K61" s="39">
+      <c r="K61" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L61" s="15">
@@ -5657,8 +5637,8 @@
       <c r="J62" s="8">
         <v>46186</v>
       </c>
-      <c r="K62" s="40">
-        <v>6733199.7699999996</v>
+      <c r="K62" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="L62" s="20">
         <v>6463871.7800000003</v>
@@ -5705,7 +5685,7 @@
       <c r="J63" s="14">
         <v>46094</v>
       </c>
-      <c r="K63" s="39">
+      <c r="K63" s="15">
         <v>6799870.4100000001</v>
       </c>
       <c r="L63" s="15">
@@ -5753,8 +5733,8 @@
       <c r="J64" s="8">
         <v>46094</v>
       </c>
-      <c r="K64" s="40">
-        <v>6733199.7699999996</v>
+      <c r="K64" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="L64" s="20">
         <v>6463871.7699999996</v>
@@ -5801,8 +5781,8 @@
       <c r="J65" s="14">
         <v>46094</v>
       </c>
-      <c r="K65" s="39">
-        <v>6733199.7699999996</v>
+      <c r="K65" s="15" t="s">
+        <v>264</v>
       </c>
       <c r="L65" s="15">
         <v>6463871.7699999996</v>
@@ -5849,7 +5829,7 @@
       <c r="J66" s="8">
         <v>46101</v>
       </c>
-      <c r="K66" s="40">
+      <c r="K66" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L66" s="20">
@@ -5897,7 +5877,7 @@
       <c r="J67" s="14">
         <v>46101</v>
       </c>
-      <c r="K67" s="39">
+      <c r="K67" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L67" s="15">
@@ -5945,7 +5925,7 @@
       <c r="J68" s="8">
         <v>46101</v>
       </c>
-      <c r="K68" s="40">
+      <c r="K68" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L68" s="20">
@@ -5993,7 +5973,7 @@
       <c r="J69" s="14">
         <v>46101</v>
       </c>
-      <c r="K69" s="39">
+      <c r="K69" s="15">
         <v>6766535.0899999999</v>
       </c>
       <c r="L69" s="15">
@@ -6041,7 +6021,7 @@
       <c r="J70" s="8">
         <v>46101</v>
       </c>
-      <c r="K70" s="40">
+      <c r="K70" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L70" s="20">
@@ -6089,7 +6069,7 @@
       <c r="J71" s="14">
         <v>46101</v>
       </c>
-      <c r="K71" s="39">
+      <c r="K71" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L71" s="15">
@@ -6137,7 +6117,7 @@
       <c r="J72" s="8">
         <v>46101</v>
       </c>
-      <c r="K72" s="40">
+      <c r="K72" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L72" s="20">
@@ -6185,7 +6165,7 @@
       <c r="J73" s="14">
         <v>46101</v>
       </c>
-      <c r="K73" s="39">
+      <c r="K73" s="15">
         <v>6733199.7699999996</v>
       </c>
       <c r="L73" s="15">
@@ -6233,8 +6213,8 @@
       <c r="J74" s="8">
         <v>46094</v>
       </c>
-      <c r="K74" s="40">
-        <v>6733199.7699999996</v>
+      <c r="K74" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="L74" s="20">
         <v>6463871.7699999996</v>
@@ -6281,8 +6261,8 @@
       <c r="J75" s="14">
         <v>46094</v>
       </c>
-      <c r="K75" s="39">
-        <v>6733199.7699999996</v>
+      <c r="K75" s="15" t="s">
+        <v>264</v>
       </c>
       <c r="L75" s="15">
         <v>6463871.7699999996</v>
@@ -6329,8 +6309,8 @@
       <c r="J76" s="8">
         <v>46094</v>
       </c>
-      <c r="K76" s="40">
-        <v>6733199.7699999996</v>
+      <c r="K76" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="L76" s="20">
         <v>6463871.7699999996</v>
@@ -6377,7 +6357,7 @@
       <c r="J77" s="14">
         <v>46094</v>
       </c>
-      <c r="K77" s="39">
+      <c r="K77" s="15">
         <v>6766535.0899999999</v>
       </c>
       <c r="L77" s="15">
@@ -6425,7 +6405,7 @@
       <c r="J78" s="8">
         <v>46094</v>
       </c>
-      <c r="K78" s="40">
+      <c r="K78" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L78" s="20">
@@ -6473,7 +6453,7 @@
       <c r="J79" s="14">
         <v>46101</v>
       </c>
-      <c r="K79" s="39">
+      <c r="K79" s="15">
         <v>6766535.0899999999</v>
       </c>
       <c r="L79" s="15">
@@ -6521,8 +6501,8 @@
       <c r="J80" s="8">
         <v>46094</v>
       </c>
-      <c r="K80" s="40">
-        <v>6733199.7699999996</v>
+      <c r="K80" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="L80" s="20">
         <v>6463871.7699999996</v>
@@ -6569,8 +6549,8 @@
       <c r="J81" s="14">
         <v>46094</v>
       </c>
-      <c r="K81" s="39">
-        <v>6733199.7699999996</v>
+      <c r="K81" s="15" t="s">
+        <v>264</v>
       </c>
       <c r="L81" s="15">
         <v>6463871.7699999996</v>
@@ -6617,7 +6597,7 @@
       <c r="J82" s="8">
         <v>46094</v>
       </c>
-      <c r="K82" s="40">
+      <c r="K82" s="20">
         <v>6766535.0899999999</v>
       </c>
       <c r="L82" s="20">
@@ -6665,8 +6645,8 @@
       <c r="J83" s="25">
         <v>46094</v>
       </c>
-      <c r="K83" s="41">
-        <v>6733199.7699999996</v>
+      <c r="K83" s="26" t="s">
+        <v>264</v>
       </c>
       <c r="L83" s="26">
         <v>6463871.7800000003</v>
@@ -6713,7 +6693,7 @@
       <c r="J84" s="8">
         <v>46100</v>
       </c>
-      <c r="K84" s="40">
+      <c r="K84" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L84" s="20">
@@ -6761,7 +6741,7 @@
       <c r="J85" s="25">
         <v>46193</v>
       </c>
-      <c r="K85" s="41">
+      <c r="K85" s="26">
         <v>6766535.0899999999</v>
       </c>
       <c r="L85" s="26">
@@ -6809,7 +6789,7 @@
       <c r="J86" s="8">
         <v>46101</v>
       </c>
-      <c r="K86" s="40">
+      <c r="K86" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L86" s="20">
@@ -6857,7 +6837,7 @@
       <c r="J87" s="25">
         <v>46100</v>
       </c>
-      <c r="K87" s="41">
+      <c r="K87" s="26">
         <v>6766535.0899999999</v>
       </c>
       <c r="L87" s="26">
@@ -6905,7 +6885,7 @@
       <c r="J88" s="8">
         <v>46101</v>
       </c>
-      <c r="K88" s="40">
+      <c r="K88" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L88" s="20">
@@ -6953,7 +6933,7 @@
       <c r="J89" s="25">
         <v>46101</v>
       </c>
-      <c r="K89" s="41">
+      <c r="K89" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L89" s="26">
@@ -7001,7 +6981,7 @@
       <c r="J90" s="8">
         <v>46101</v>
       </c>
-      <c r="K90" s="40">
+      <c r="K90" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L90" s="20">
@@ -7049,7 +7029,7 @@
       <c r="J91" s="25">
         <v>46101</v>
       </c>
-      <c r="K91" s="41">
+      <c r="K91" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L91" s="26">
@@ -7097,7 +7077,7 @@
       <c r="J92" s="8">
         <v>46185</v>
       </c>
-      <c r="K92" s="40">
+      <c r="K92" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L92" s="20">
@@ -7145,7 +7125,7 @@
       <c r="J93" s="25">
         <v>46288</v>
       </c>
-      <c r="K93" s="41">
+      <c r="K93" s="26">
         <v>6766535.0899999999</v>
       </c>
       <c r="L93" s="26">
@@ -7193,7 +7173,7 @@
       <c r="J94" s="8">
         <v>46182</v>
       </c>
-      <c r="K94" s="40">
+      <c r="K94" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L94" s="20">
@@ -7241,7 +7221,7 @@
       <c r="J95" s="25">
         <v>46300</v>
       </c>
-      <c r="K95" s="41">
+      <c r="K95" s="26">
         <v>6866541.0599999996</v>
       </c>
       <c r="L95" s="26">
@@ -7289,7 +7269,7 @@
       <c r="J96" s="8">
         <v>46182</v>
       </c>
-      <c r="K96" s="40">
+      <c r="K96" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L96" s="20">
@@ -7337,7 +7317,7 @@
       <c r="J97" s="25">
         <v>46185</v>
       </c>
-      <c r="K97" s="41">
+      <c r="K97" s="26">
         <v>6766535.0899999999</v>
       </c>
       <c r="L97" s="26">
@@ -7385,7 +7365,7 @@
       <c r="J98" s="8">
         <v>46185</v>
       </c>
-      <c r="K98" s="40">
+      <c r="K98" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L98" s="20">
@@ -7433,7 +7413,7 @@
       <c r="J99" s="25">
         <v>46321</v>
       </c>
-      <c r="K99" s="41">
+      <c r="K99" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L99" s="26">
@@ -7481,7 +7461,7 @@
       <c r="J100" s="8">
         <v>46196</v>
       </c>
-      <c r="K100" s="40">
+      <c r="K100" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L100" s="20">
@@ -7529,7 +7509,7 @@
       <c r="J101" s="25">
         <v>46159</v>
       </c>
-      <c r="K101" s="41">
+      <c r="K101" s="26">
         <v>2978833.7</v>
       </c>
       <c r="L101" s="26">
@@ -7539,7 +7519,7 @@
         <v>178731</v>
       </c>
       <c r="N101" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" s="11">
         <v>0</v>
@@ -7577,7 +7557,7 @@
       <c r="J102" s="8">
         <v>46159</v>
       </c>
-      <c r="K102" s="40">
+      <c r="K102" s="20">
         <v>4815813.57</v>
       </c>
       <c r="L102" s="20">
@@ -7587,7 +7567,7 @@
         <v>288949</v>
       </c>
       <c r="N102" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O102" s="11">
         <v>0</v>
@@ -7625,7 +7605,7 @@
       <c r="J103" s="25">
         <v>46201</v>
       </c>
-      <c r="K103" s="41">
+      <c r="K103" s="26">
         <v>10267612.310000001</v>
       </c>
       <c r="L103" s="26">
@@ -7673,7 +7653,7 @@
       <c r="J104" s="8">
         <v>46188</v>
       </c>
-      <c r="K104" s="40">
+      <c r="K104" s="20">
         <v>4522636.47</v>
       </c>
       <c r="L104" s="20">
@@ -7721,7 +7701,7 @@
       <c r="J105" s="25">
         <v>46321</v>
       </c>
-      <c r="K105" s="41">
+      <c r="K105" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L105" s="26">
@@ -7769,7 +7749,7 @@
       <c r="J106" s="8">
         <v>46343</v>
       </c>
-      <c r="K106" s="40">
+      <c r="K106" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L106" s="20">
@@ -7817,7 +7797,7 @@
       <c r="J107" s="25">
         <v>46263</v>
       </c>
-      <c r="K107" s="41">
+      <c r="K107" s="26">
         <v>7538159.6500000004</v>
       </c>
       <c r="L107" s="26">
@@ -7865,7 +7845,7 @@
       <c r="J108" s="8">
         <v>46206</v>
       </c>
-      <c r="K108" s="40">
+      <c r="K108" s="20">
         <v>1361476.58</v>
       </c>
       <c r="L108" s="20">
@@ -7913,7 +7893,7 @@
       <c r="J109" s="25">
         <v>46354</v>
       </c>
-      <c r="K109" s="41">
+      <c r="K109" s="26">
         <v>7919384.8899999997</v>
       </c>
       <c r="L109" s="26">
@@ -7961,7 +7941,7 @@
       <c r="J110" s="8">
         <v>46263</v>
       </c>
-      <c r="K110" s="40">
+      <c r="K110" s="20">
         <v>9644036.5700000003</v>
       </c>
       <c r="L110" s="20">
@@ -7971,7 +7951,7 @@
         <v>385761.46</v>
       </c>
       <c r="N110" s="18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O110" s="11">
         <v>0</v>
@@ -8009,7 +7989,7 @@
       <c r="J111" s="25">
         <v>46270</v>
       </c>
-      <c r="K111" s="41">
+      <c r="K111" s="26">
         <v>5987622.7699999996</v>
       </c>
       <c r="L111" s="26">
@@ -8019,7 +7999,7 @@
         <v>239504.93</v>
       </c>
       <c r="N111" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O111" s="11">
         <v>0</v>
@@ -8057,7 +8037,7 @@
       <c r="J112" s="8">
         <v>46171</v>
       </c>
-      <c r="K112" s="40">
+      <c r="K112" s="20">
         <v>7597380.0999999996</v>
       </c>
       <c r="L112" s="20">
@@ -8105,7 +8085,7 @@
       <c r="J113" s="25">
         <v>46355</v>
       </c>
-      <c r="K113" s="41">
+      <c r="K113" s="26">
         <v>7085292.8899999997</v>
       </c>
       <c r="L113" s="26">
@@ -8153,7 +8133,7 @@
       <c r="J114" s="8">
         <v>46270</v>
       </c>
-      <c r="K114" s="40">
+      <c r="K114" s="20">
         <v>5936392.6299999999</v>
       </c>
       <c r="L114" s="20">
@@ -8201,7 +8181,7 @@
       <c r="J115" s="25">
         <v>46118</v>
       </c>
-      <c r="K115" s="41">
+      <c r="K115" s="26">
         <v>6098569.0300000003</v>
       </c>
       <c r="L115" s="26">
@@ -8249,7 +8229,7 @@
       <c r="J116" s="8">
         <v>46202</v>
       </c>
-      <c r="K116" s="40">
+      <c r="K116" s="20">
         <v>10111644.16</v>
       </c>
       <c r="L116" s="20">
@@ -8297,7 +8277,7 @@
       <c r="J117" s="25">
         <v>46287</v>
       </c>
-      <c r="K117" s="41">
+      <c r="K117" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L117" s="26">
@@ -8345,7 +8325,7 @@
       <c r="J118" s="8">
         <v>46280</v>
       </c>
-      <c r="K118" s="40">
+      <c r="K118" s="20">
         <v>7905250.0099999998</v>
       </c>
       <c r="L118" s="20">
@@ -8393,7 +8373,7 @@
       <c r="J119" s="25">
         <v>46287</v>
       </c>
-      <c r="K119" s="41">
+      <c r="K119" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L119" s="26">
@@ -8441,7 +8421,7 @@
       <c r="J120" s="8">
         <v>46297</v>
       </c>
-      <c r="K120" s="40">
+      <c r="K120" s="20">
         <v>7433497.3700000001</v>
       </c>
       <c r="L120" s="20">
@@ -8489,7 +8469,7 @@
       <c r="J121" s="25">
         <v>46385</v>
       </c>
-      <c r="K121" s="41">
+      <c r="K121" s="26">
         <v>8109449.7199999997</v>
       </c>
       <c r="L121" s="26">
@@ -8537,7 +8517,7 @@
       <c r="J122" s="8">
         <v>46287</v>
       </c>
-      <c r="K122" s="40">
+      <c r="K122" s="20">
         <v>6733199.7699999996</v>
       </c>
       <c r="L122" s="20">
@@ -8585,7 +8565,7 @@
       <c r="J123" s="25">
         <v>46378</v>
       </c>
-      <c r="K123" s="41">
+      <c r="K123" s="26">
         <v>6733199.7699999996</v>
       </c>
       <c r="L123" s="26">
@@ -8633,7 +8613,7 @@
       <c r="J124" s="8">
         <v>46294</v>
       </c>
-      <c r="K124" s="40">
+      <c r="K124" s="20">
         <v>8549857.9499999993</v>
       </c>
       <c r="L124" s="20">
@@ -8681,7 +8661,7 @@
       <c r="J125" s="25">
         <v>46202</v>
       </c>
-      <c r="K125" s="41">
+      <c r="K125" s="26">
         <v>4451199.25</v>
       </c>
       <c r="L125" s="26">
@@ -8729,7 +8709,7 @@
       <c r="J126" s="8">
         <v>46199</v>
       </c>
-      <c r="K126" s="40">
+      <c r="K126" s="20">
         <v>448663.59</v>
       </c>
       <c r="L126" s="20">
@@ -8777,7 +8757,7 @@
       <c r="J127" s="25">
         <v>46294</v>
       </c>
-      <c r="K127" s="41">
+      <c r="K127" s="26">
         <v>6669499.3600000003</v>
       </c>
       <c r="L127" s="26">
@@ -8825,7 +8805,7 @@
       <c r="J128" s="8">
         <v>46205</v>
       </c>
-      <c r="K128" s="40">
+      <c r="K128" s="20">
         <v>3691957.2</v>
       </c>
       <c r="L128" s="20">
@@ -8873,7 +8853,7 @@
       <c r="J129" s="25">
         <v>46385</v>
       </c>
-      <c r="K129" s="41">
+      <c r="K129" s="26">
         <v>5841288.4000000004</v>
       </c>
       <c r="L129" s="26">
@@ -8921,7 +8901,7 @@
       <c r="J130" s="8">
         <v>46202</v>
       </c>
-      <c r="K130" s="40">
+      <c r="K130" s="20">
         <v>2664074.9</v>
       </c>
       <c r="L130" s="20">
@@ -8969,7 +8949,7 @@
       <c r="J131" s="25">
         <v>46202</v>
       </c>
-      <c r="K131" s="41">
+      <c r="K131" s="26">
         <v>4381733.59</v>
       </c>
       <c r="L131" s="26">
@@ -9017,7 +8997,7 @@
       <c r="J132" s="8">
         <v>46294</v>
       </c>
-      <c r="K132" s="40">
+      <c r="K132" s="20">
         <v>6619448.9500000002</v>
       </c>
       <c r="L132" s="20">
@@ -9065,7 +9045,7 @@
       <c r="J133" s="25">
         <v>46385</v>
       </c>
-      <c r="K133" s="41">
+      <c r="K133" s="26">
         <v>7147392.5</v>
       </c>
       <c r="L133" s="26">
@@ -9113,7 +9093,7 @@
       <c r="J134" s="8">
         <v>46205</v>
       </c>
-      <c r="K134" s="40">
+      <c r="K134" s="20">
         <v>4049587.48</v>
       </c>
       <c r="L134" s="20">
@@ -9134,7 +9114,7 @@
         <v>0</v>
       </c>
       <c r="B135" s="24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C135" s="24" t="s">
         <v>577</v>
@@ -9161,7 +9141,7 @@
       <c r="J135" s="25">
         <v>46297</v>
       </c>
-      <c r="K135" s="41">
+      <c r="K135" s="26">
         <v>7774378.9000000004</v>
       </c>
       <c r="L135" s="26">
@@ -9209,7 +9189,7 @@
       <c r="J136" s="8">
         <v>46206</v>
       </c>
-      <c r="K136" s="40">
+      <c r="K136" s="20">
         <v>8098553.8300000001</v>
       </c>
       <c r="L136" s="20">
@@ -9257,7 +9237,7 @@
       <c r="J137" s="25">
         <v>46391</v>
       </c>
-      <c r="K137" s="41">
+      <c r="K137" s="26">
         <v>6475379.0599999996</v>
       </c>
       <c r="L137" s="26">
@@ -9305,7 +9285,7 @@
       <c r="J138" s="8">
         <v>46391</v>
       </c>
-      <c r="K138" s="40">
+      <c r="K138" s="20">
         <v>15675584.369999999</v>
       </c>
       <c r="L138" s="20">
@@ -9326,10 +9306,10 @@
         <v>0</v>
       </c>
       <c r="B139" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C139" s="24" t="s">
         <v>235</v>
-      </c>
-      <c r="C139" s="24" t="s">
-        <v>236</v>
       </c>
       <c r="D139" s="24" t="s">
         <v>590</v>
@@ -9353,7 +9333,7 @@
       <c r="J139" s="25">
         <v>46206</v>
       </c>
-      <c r="K139" s="41">
+      <c r="K139" s="26">
         <v>6947110.9199999999</v>
       </c>
       <c r="L139" s="26">
@@ -9401,7 +9381,7 @@
       <c r="J140" s="8">
         <v>46391</v>
       </c>
-      <c r="K140" s="40">
+      <c r="K140" s="20">
         <v>6008903.5</v>
       </c>
       <c r="L140" s="20">
@@ -9449,7 +9429,7 @@
       <c r="J141" s="25">
         <v>46391</v>
       </c>
-      <c r="K141" s="41">
+      <c r="K141" s="26">
         <v>5137667.07</v>
       </c>
       <c r="L141" s="26">
@@ -9497,7 +9477,7 @@
       <c r="J142" s="8">
         <v>46299</v>
       </c>
-      <c r="K142" s="40">
+      <c r="K142" s="20">
         <v>4749769.6500000004</v>
       </c>
       <c r="L142" s="20">
@@ -9521,7 +9501,7 @@
         <v>77</v>
       </c>
       <c r="C143" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D143" s="24" t="s">
         <v>602</v>
@@ -9545,7 +9525,7 @@
       <c r="J143" s="25">
         <v>46207</v>
       </c>
-      <c r="K143" s="41">
+      <c r="K143" s="26">
         <v>5209082.62</v>
       </c>
       <c r="L143" s="26">
@@ -9593,7 +9573,7 @@
       <c r="J144" s="8">
         <v>46299</v>
       </c>
-      <c r="K144" s="40">
+      <c r="K144" s="20">
         <v>16880259.960000001</v>
       </c>
       <c r="L144" s="20">
@@ -9614,10 +9594,10 @@
         <v>0</v>
       </c>
       <c r="B145" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C145" s="24" t="s">
         <v>253</v>
-      </c>
-      <c r="C145" s="24" t="s">
-        <v>254</v>
       </c>
       <c r="D145" s="24" t="s">
         <v>608</v>
@@ -9641,7 +9621,7 @@
       <c r="J145" s="25">
         <v>46435</v>
       </c>
-      <c r="K145" s="41">
+      <c r="K145" s="26">
         <v>5168308.1100000003</v>
       </c>
       <c r="L145" s="26">
@@ -9689,7 +9669,7 @@
       <c r="J146" s="31">
         <v>46326</v>
       </c>
-      <c r="K146" s="42">
+      <c r="K146" s="32">
         <v>240000</v>
       </c>
       <c r="L146" s="32">
@@ -16827,7 +16807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F582"/>
+  <dimension ref="A1:F588"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -18227,7 +18207,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -18241,7 +18221,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -18255,7 +18235,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B95">
         <v>3</v>
@@ -18337,7 +18317,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -18351,7 +18331,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -18365,7 +18345,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B102">
         <v>3</v>
@@ -18492,7 +18472,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -18506,7 +18486,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B111">
         <v>2</v>
@@ -18520,7 +18500,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -18618,7 +18598,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -18632,7 +18612,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -18646,7 +18626,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B121">
         <v>3</v>
@@ -18778,7 +18758,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -18795,7 +18775,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B131">
         <v>2</v>
@@ -18812,7 +18792,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -18888,7 +18868,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -18905,7 +18885,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -18919,7 +18899,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B139">
         <v>3</v>
@@ -19020,7 +19000,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -19034,7 +19014,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B147">
         <v>2</v>
@@ -19048,7 +19028,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B148">
         <v>3</v>
@@ -19236,7 +19216,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -19250,7 +19230,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B162">
         <v>2</v>
@@ -19264,7 +19244,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B163">
         <v>3</v>
@@ -19405,7 +19385,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -19419,7 +19399,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B173">
         <v>2</v>
@@ -19433,7 +19413,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B174">
         <v>3</v>
@@ -19678,7 +19658,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -19695,7 +19675,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B191">
         <v>2</v>
@@ -19712,7 +19692,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B192">
         <v>3</v>
@@ -19768,7 +19748,7 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -19782,7 +19762,7 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B197">
         <v>2</v>
@@ -19796,7 +19776,7 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B198">
         <v>3</v>
@@ -19922,7 +19902,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -19936,7 +19916,7 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -19950,7 +19930,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B209">
         <v>3</v>
@@ -20006,7 +19986,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -20023,7 +20003,7 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B214">
         <v>2</v>
@@ -20040,7 +20020,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B215">
         <v>3</v>
@@ -20152,7 +20132,7 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -20169,7 +20149,7 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B224">
         <v>2</v>
@@ -20186,7 +20166,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B225">
         <v>3</v>
@@ -20354,7 +20334,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -20368,7 +20348,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B238">
         <v>2</v>
@@ -20382,7 +20362,7 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B239">
         <v>3</v>
@@ -22281,16 +22261,19 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>574</v>
+        <v>300</v>
       </c>
       <c r="B365">
-        <v>1</v>
-      </c>
-      <c r="C365" s="1">
-        <v>194380.2</v>
+        <v>4</v>
+      </c>
+      <c r="C365" s="37">
+        <v>659331.79</v>
+      </c>
+      <c r="D365" s="37">
+        <v>659331.79</v>
       </c>
       <c r="F365" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -22298,10 +22281,10 @@
         <v>574</v>
       </c>
       <c r="B366">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C366" s="1">
-        <v>923305.95</v>
+        <v>194380.2</v>
       </c>
       <c r="F366" t="s">
         <v>636</v>
@@ -22312,7 +22295,7 @@
         <v>574</v>
       </c>
       <c r="B367">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C367" s="1">
         <v>923305.95</v>
@@ -22326,10 +22309,10 @@
         <v>574</v>
       </c>
       <c r="B368">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C368" s="1">
-        <v>923305.94</v>
+        <v>923305.95</v>
       </c>
       <c r="F368" t="s">
         <v>636</v>
@@ -22340,7 +22323,7 @@
         <v>574</v>
       </c>
       <c r="B369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C369" s="1">
         <v>923305.94</v>
@@ -22351,19 +22334,16 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>303</v>
+        <v>574</v>
       </c>
       <c r="B370">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C370" s="1">
-        <v>2165291.23</v>
-      </c>
-      <c r="D370" s="1">
-        <v>2165291.23</v>
+        <v>923305.94</v>
       </c>
       <c r="F370" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -22371,7 +22351,7 @@
         <v>303</v>
       </c>
       <c r="B371">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C371" s="1">
         <v>2165291.23</v>
@@ -22388,24 +22368,27 @@
         <v>303</v>
       </c>
       <c r="B372">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C372" s="1">
         <v>2165291.23</v>
       </c>
+      <c r="D372" s="1">
+        <v>2165291.23</v>
+      </c>
       <c r="F372" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>578</v>
+        <v>303</v>
       </c>
       <c r="B373">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C373" s="1">
-        <v>369283</v>
+        <v>2165291.23</v>
       </c>
       <c r="F373" t="s">
         <v>636</v>
@@ -22416,10 +22399,10 @@
         <v>578</v>
       </c>
       <c r="B374">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C374" s="1">
-        <v>1403275.39</v>
+        <v>369283</v>
       </c>
       <c r="F374" t="s">
         <v>636</v>
@@ -22430,7 +22413,7 @@
         <v>578</v>
       </c>
       <c r="B375">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C375" s="1">
         <v>1403275.39</v>
@@ -22444,7 +22427,7 @@
         <v>578</v>
       </c>
       <c r="B376">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C376" s="1">
         <v>1403275.39</v>
@@ -22458,7 +22441,7 @@
         <v>578</v>
       </c>
       <c r="B377">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C377" s="1">
         <v>1403275.39</v>
@@ -22472,7 +22455,7 @@
         <v>578</v>
       </c>
       <c r="B378">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C378" s="1">
         <v>1403275.39</v>
@@ -22483,19 +22466,16 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>19</v>
+        <v>578</v>
       </c>
       <c r="B379">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C379" s="1">
-        <v>38075.75</v>
-      </c>
-      <c r="D379" s="1">
-        <v>38075.75</v>
+        <v>1403275.39</v>
       </c>
       <c r="F379" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -22503,13 +22483,13 @@
         <v>19</v>
       </c>
       <c r="B380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C380" s="1">
-        <v>91308.33</v>
+        <v>38075.75</v>
       </c>
       <c r="D380" s="1">
-        <v>91308.33</v>
+        <v>38075.75</v>
       </c>
       <c r="F380" t="s">
         <v>635</v>
@@ -22520,13 +22500,13 @@
         <v>19</v>
       </c>
       <c r="B381">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C381" s="1">
-        <v>152459.75</v>
+        <v>91308.33</v>
       </c>
       <c r="D381" s="1">
-        <v>152459.75</v>
+        <v>91308.33</v>
       </c>
       <c r="F381" t="s">
         <v>635</v>
@@ -22537,13 +22517,13 @@
         <v>19</v>
       </c>
       <c r="B382">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C382" s="1">
-        <v>328874.09999999998</v>
+        <v>152459.75</v>
       </c>
       <c r="D382" s="1">
-        <v>328874.09999999998</v>
+        <v>152459.75</v>
       </c>
       <c r="F382" t="s">
         <v>635</v>
@@ -22554,13 +22534,16 @@
         <v>19</v>
       </c>
       <c r="B383">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C383" s="1">
-        <v>512868.36</v>
+        <v>328874.09999999998</v>
+      </c>
+      <c r="D383" s="1">
+        <v>328874.09999999998</v>
       </c>
       <c r="F383" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -22568,10 +22551,10 @@
         <v>19</v>
       </c>
       <c r="B384">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C384" s="1">
-        <v>526075.59</v>
+        <v>512868.36</v>
       </c>
       <c r="F384" t="s">
         <v>636</v>
@@ -22582,30 +22565,30 @@
         <v>19</v>
       </c>
       <c r="B385">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C385" s="1">
-        <v>433259.1</v>
-      </c>
-      <c r="D385" s="1">
-        <v>433259.1</v>
+        <v>526075.59</v>
       </c>
       <c r="F385" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="B386">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C386" s="1">
-        <v>706912.64</v>
+        <v>433259.1</v>
+      </c>
+      <c r="D386" s="1">
+        <v>433259.1</v>
       </c>
       <c r="F386" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -22613,7 +22596,7 @@
         <v>112</v>
       </c>
       <c r="B387">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C387" s="1">
         <v>706912.64</v>
@@ -22627,7 +22610,7 @@
         <v>112</v>
       </c>
       <c r="B388">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C388" s="1">
         <v>706912.64</v>
@@ -22641,7 +22624,7 @@
         <v>112</v>
       </c>
       <c r="B389">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C389" s="1">
         <v>706912.64</v>
@@ -22655,7 +22638,7 @@
         <v>112</v>
       </c>
       <c r="B390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C390" s="1">
         <v>706912.64</v>
@@ -22669,10 +22652,10 @@
         <v>112</v>
       </c>
       <c r="B391">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C391" s="1">
-        <v>706912.63</v>
+        <v>706912.64</v>
       </c>
       <c r="F391" t="s">
         <v>636</v>
@@ -22680,19 +22663,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="B392">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C392" s="1">
-        <v>2120181.0099999998</v>
-      </c>
-      <c r="D392" s="1">
-        <v>2120181.0099999998</v>
+        <v>706912.63</v>
       </c>
       <c r="F392" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -22700,13 +22680,16 @@
         <v>306</v>
       </c>
       <c r="B393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C393" s="1">
         <v>2120181.0099999998</v>
       </c>
+      <c r="D393" s="1">
+        <v>2120181.0099999998</v>
+      </c>
       <c r="F393" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -22714,7 +22697,7 @@
         <v>306</v>
       </c>
       <c r="B394">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C394" s="1">
         <v>2120181.0099999998</v>
@@ -22725,13 +22708,13 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>581</v>
+        <v>306</v>
       </c>
       <c r="B395">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C395" s="1">
-        <v>388730.58</v>
+        <v>2120181.0099999998</v>
       </c>
       <c r="F395" t="s">
         <v>636</v>
@@ -22742,10 +22725,10 @@
         <v>581</v>
       </c>
       <c r="B396">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C396" s="1">
-        <v>1477176.22</v>
+        <v>388730.58</v>
       </c>
       <c r="F396" t="s">
         <v>636</v>
@@ -22756,7 +22739,7 @@
         <v>581</v>
       </c>
       <c r="B397">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C397" s="1">
         <v>1477176.22</v>
@@ -22770,7 +22753,7 @@
         <v>581</v>
       </c>
       <c r="B398">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C398" s="1">
         <v>1477176.22</v>
@@ -22784,7 +22767,7 @@
         <v>581</v>
       </c>
       <c r="B399">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C399" s="1">
         <v>1477176.22</v>
@@ -22798,10 +22781,10 @@
         <v>581</v>
       </c>
       <c r="B400">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C400" s="1">
-        <v>1477176.2</v>
+        <v>1477176.22</v>
       </c>
       <c r="F400" t="s">
         <v>636</v>
@@ -22809,19 +22792,16 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>309</v>
+        <v>581</v>
       </c>
       <c r="B401">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C401" s="1">
-        <v>2154623.9300000002</v>
-      </c>
-      <c r="D401" s="1">
-        <v>2154623.9300000002</v>
+        <v>1477176.2</v>
       </c>
       <c r="F401" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -22829,7 +22809,7 @@
         <v>309</v>
       </c>
       <c r="B402">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C402" s="1">
         <v>2154623.9300000002</v>
@@ -22846,30 +22826,30 @@
         <v>309</v>
       </c>
       <c r="B403">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C403" s="1">
         <v>2154623.9300000002</v>
       </c>
+      <c r="D403" s="1">
+        <v>2154623.9300000002</v>
+      </c>
       <c r="F403" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>584</v>
+        <v>309</v>
       </c>
       <c r="B404">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C404" s="1">
-        <v>307580.5</v>
-      </c>
-      <c r="D404" s="1">
-        <v>307580.5</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F404" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -22877,13 +22857,13 @@
         <v>584</v>
       </c>
       <c r="B405">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C405" s="1">
-        <v>1461007.4</v>
+        <v>307580.5</v>
       </c>
       <c r="D405" s="1">
-        <v>1461007.4</v>
+        <v>307580.5</v>
       </c>
       <c r="F405" t="s">
         <v>635</v>
@@ -22894,13 +22874,16 @@
         <v>584</v>
       </c>
       <c r="B406">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C406" s="1">
         <v>1461007.4</v>
       </c>
+      <c r="D406" s="1">
+        <v>1461007.4</v>
+      </c>
       <c r="F406" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -22908,7 +22891,7 @@
         <v>584</v>
       </c>
       <c r="B407">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C407" s="1">
         <v>1461007.4</v>
@@ -22922,7 +22905,7 @@
         <v>584</v>
       </c>
       <c r="B408">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C408" s="1">
         <v>1461007.4</v>
@@ -22933,19 +22916,16 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>312</v>
+        <v>584</v>
       </c>
       <c r="B409">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C409" s="1">
-        <v>2197716.42</v>
-      </c>
-      <c r="D409" s="1">
-        <v>2197716.42</v>
+        <v>1461007.4</v>
       </c>
       <c r="F409" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22953,13 +22933,16 @@
         <v>312</v>
       </c>
       <c r="B410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C410" s="1">
-        <v>2133077.6800000002</v>
+        <v>2197716.42</v>
+      </c>
+      <c r="D410" s="1">
+        <v>2197716.42</v>
       </c>
       <c r="F410" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22967,7 +22950,7 @@
         <v>312</v>
       </c>
       <c r="B411">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C411" s="1">
         <v>2133077.6800000002</v>
@@ -22978,13 +22961,13 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>587</v>
+        <v>312</v>
       </c>
       <c r="B412">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C412" s="1">
-        <v>752428.03</v>
+        <v>2133077.6800000002</v>
       </c>
       <c r="F412" t="s">
         <v>636</v>
@@ -22995,10 +22978,10 @@
         <v>587</v>
       </c>
       <c r="B413">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C413" s="1">
-        <v>2042304.71</v>
+        <v>752428.03</v>
       </c>
       <c r="F413" t="s">
         <v>636</v>
@@ -23009,7 +22992,7 @@
         <v>587</v>
       </c>
       <c r="B414">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C414" s="1">
         <v>2042304.71</v>
@@ -23023,7 +23006,7 @@
         <v>587</v>
       </c>
       <c r="B415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C415" s="1">
         <v>2042304.71</v>
@@ -23037,7 +23020,7 @@
         <v>587</v>
       </c>
       <c r="B416">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C416" s="1">
         <v>2042304.71</v>
@@ -23051,7 +23034,7 @@
         <v>587</v>
       </c>
       <c r="B417">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C417" s="1">
         <v>2042304.71</v>
@@ -23065,7 +23048,7 @@
         <v>587</v>
       </c>
       <c r="B418">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C418" s="1">
         <v>2042304.71</v>
@@ -23079,7 +23062,7 @@
         <v>587</v>
       </c>
       <c r="B419">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C419" s="1">
         <v>2042304.71</v>
@@ -23090,19 +23073,16 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>117</v>
+        <v>587</v>
       </c>
       <c r="B420">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C420" s="1">
-        <v>698708.05</v>
-      </c>
-      <c r="D420" s="1">
-        <v>698708.05</v>
+        <v>2042304.71</v>
       </c>
       <c r="F420" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -23110,7 +23090,7 @@
         <v>117</v>
       </c>
       <c r="B421">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C421" s="1">
         <v>698708.05</v>
@@ -23127,7 +23107,7 @@
         <v>117</v>
       </c>
       <c r="B422">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C422" s="1">
         <v>698708.05</v>
@@ -23144,7 +23124,7 @@
         <v>117</v>
       </c>
       <c r="B423">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C423" s="1">
         <v>698708.05</v>
@@ -23161,7 +23141,7 @@
         <v>117</v>
       </c>
       <c r="B424">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C424" s="1">
         <v>698708.05</v>
@@ -23178,7 +23158,7 @@
         <v>117</v>
       </c>
       <c r="B425">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C425" s="1">
         <v>698708.05</v>
@@ -23192,16 +23172,16 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>317</v>
+        <v>117</v>
       </c>
       <c r="B426">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C426" s="1">
-        <v>2142736.11</v>
+        <v>698708.05</v>
       </c>
       <c r="D426" s="1">
-        <v>2142736.11</v>
+        <v>698708.05</v>
       </c>
       <c r="F426" t="s">
         <v>635</v>
@@ -23212,7 +23192,7 @@
         <v>317</v>
       </c>
       <c r="B427">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C427" s="1">
         <v>2142736.11</v>
@@ -23229,13 +23209,13 @@
         <v>317</v>
       </c>
       <c r="B428">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C428" s="1">
-        <v>2142736.12</v>
+        <v>2142736.11</v>
       </c>
       <c r="D428" s="1">
-        <v>2142736.12</v>
+        <v>2142736.11</v>
       </c>
       <c r="F428" t="s">
         <v>635</v>
@@ -23243,16 +23223,19 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>590</v>
+        <v>317</v>
       </c>
       <c r="B429">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C429" s="1">
-        <v>333461.32</v>
+        <v>2142736.12</v>
+      </c>
+      <c r="D429" s="1">
+        <v>2142736.12</v>
       </c>
       <c r="F429" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -23260,10 +23243,10 @@
         <v>590</v>
       </c>
       <c r="B430">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C430" s="1">
-        <v>1583941.29</v>
+        <v>333461.32</v>
       </c>
       <c r="F430" t="s">
         <v>636</v>
@@ -23274,7 +23257,7 @@
         <v>590</v>
       </c>
       <c r="B431">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C431" s="1">
         <v>1583941.29</v>
@@ -23288,7 +23271,7 @@
         <v>590</v>
       </c>
       <c r="B432">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C432" s="1">
         <v>1583941.29</v>
@@ -23302,7 +23285,7 @@
         <v>590</v>
       </c>
       <c r="B433">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C433" s="1">
         <v>1583941.29</v>
@@ -23313,19 +23296,16 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>322</v>
+        <v>590</v>
       </c>
       <c r="B434">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C434" s="1">
-        <v>2154623.92</v>
-      </c>
-      <c r="D434" s="1">
-        <v>2154623.92</v>
+        <v>1583941.29</v>
       </c>
       <c r="F434" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -23333,13 +23313,13 @@
         <v>322</v>
       </c>
       <c r="B435">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C435" s="1">
-        <v>2154623.923</v>
+        <v>2154623.92</v>
       </c>
       <c r="D435" s="1">
-        <v>2154623.923</v>
+        <v>2154623.92</v>
       </c>
       <c r="F435" t="s">
         <v>635</v>
@@ -23350,13 +23330,13 @@
         <v>322</v>
       </c>
       <c r="B436">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C436" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.923</v>
       </c>
       <c r="D436" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.923</v>
       </c>
       <c r="F436" t="s">
         <v>635</v>
@@ -23364,16 +23344,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
       <c r="B437">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C437" s="1">
-        <v>282404.34000000003</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="D437" s="1">
-        <v>282404.34000000003</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F437" t="s">
         <v>635</v>
@@ -23384,13 +23364,13 @@
         <v>122</v>
       </c>
       <c r="B438">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C438" s="1">
-        <v>282404.33</v>
+        <v>282404.34000000003</v>
       </c>
       <c r="D438" s="1">
-        <v>282404.33</v>
+        <v>282404.34000000003</v>
       </c>
       <c r="F438" t="s">
         <v>635</v>
@@ -23401,13 +23381,16 @@
         <v>122</v>
       </c>
       <c r="B439">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C439" s="1">
         <v>282404.33</v>
       </c>
+      <c r="D439" s="1">
+        <v>282404.33</v>
+      </c>
       <c r="F439" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -23415,30 +23398,27 @@
         <v>122</v>
       </c>
       <c r="B440">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C440" s="1">
         <v>282404.33</v>
       </c>
-      <c r="D440" s="1">
-        <v>282404.33</v>
-      </c>
       <c r="F440" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>327</v>
+        <v>122</v>
       </c>
       <c r="B441">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C441" s="1">
-        <v>2154623.92</v>
+        <v>282404.33</v>
       </c>
       <c r="D441" s="1">
-        <v>2154623.92</v>
+        <v>282404.33</v>
       </c>
       <c r="F441" t="s">
         <v>635</v>
@@ -23449,13 +23429,16 @@
         <v>327</v>
       </c>
       <c r="B442">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C442" s="1">
         <v>2154623.92</v>
       </c>
+      <c r="D442" s="1">
+        <v>2154623.92</v>
+      </c>
       <c r="F442" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -23463,10 +23446,10 @@
         <v>327</v>
       </c>
       <c r="B443">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C443" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.92</v>
       </c>
       <c r="F443" t="s">
         <v>636</v>
@@ -23474,13 +23457,13 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>593</v>
+        <v>327</v>
       </c>
       <c r="B444">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C444" s="1">
-        <v>288427.36</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F444" t="s">
         <v>636</v>
@@ -23491,10 +23474,10 @@
         <v>593</v>
       </c>
       <c r="B445">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C445" s="1">
-        <v>1370029.98</v>
+        <v>288427.36</v>
       </c>
       <c r="F445" t="s">
         <v>636</v>
@@ -23505,7 +23488,7 @@
         <v>593</v>
       </c>
       <c r="B446">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C446" s="1">
         <v>1370029.98</v>
@@ -23519,7 +23502,7 @@
         <v>593</v>
       </c>
       <c r="B447">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C447" s="1">
         <v>1370029.98</v>
@@ -23533,10 +23516,10 @@
         <v>593</v>
       </c>
       <c r="B448">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C448" s="1">
-        <v>1370030</v>
+        <v>1370029.98</v>
       </c>
       <c r="F448" t="s">
         <v>636</v>
@@ -23544,13 +23527,13 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>127</v>
+        <v>593</v>
       </c>
       <c r="B449">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C449" s="1">
-        <v>335342.49</v>
+        <v>1370030</v>
       </c>
       <c r="F449" t="s">
         <v>636</v>
@@ -23561,10 +23544,10 @@
         <v>127</v>
       </c>
       <c r="B450">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C450" s="1">
-        <v>335342.48</v>
+        <v>335342.49</v>
       </c>
       <c r="F450" t="s">
         <v>636</v>
@@ -23575,7 +23558,7 @@
         <v>127</v>
       </c>
       <c r="B451">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C451" s="1">
         <v>335342.48</v>
@@ -23589,7 +23572,7 @@
         <v>127</v>
       </c>
       <c r="B452">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C452" s="1">
         <v>335342.48</v>
@@ -23603,7 +23586,7 @@
         <v>127</v>
       </c>
       <c r="B453">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C453" s="1">
         <v>335342.48</v>
@@ -23617,7 +23600,7 @@
         <v>127</v>
       </c>
       <c r="B454">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C454" s="1">
         <v>335342.48</v>
@@ -23628,13 +23611,13 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>332</v>
+        <v>127</v>
       </c>
       <c r="B455">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C455" s="1">
-        <v>2154623.92</v>
+        <v>335342.48</v>
       </c>
       <c r="F455" t="s">
         <v>636</v>
@@ -23645,7 +23628,7 @@
         <v>332</v>
       </c>
       <c r="B456">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C456" s="1">
         <v>2154623.92</v>
@@ -23659,10 +23642,10 @@
         <v>332</v>
       </c>
       <c r="B457">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C457" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.92</v>
       </c>
       <c r="F457" t="s">
         <v>636</v>
@@ -23670,13 +23653,13 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>596</v>
+        <v>332</v>
       </c>
       <c r="B458">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C458" s="1">
-        <v>246608.02</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F458" t="s">
         <v>636</v>
@@ -23687,10 +23670,10 @@
         <v>596</v>
       </c>
       <c r="B459">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C459" s="1">
-        <v>1171388.0900000001</v>
+        <v>246608.02</v>
       </c>
       <c r="F459" t="s">
         <v>636</v>
@@ -23701,7 +23684,7 @@
         <v>596</v>
       </c>
       <c r="B460">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C460" s="1">
         <v>1171388.0900000001</v>
@@ -23715,7 +23698,7 @@
         <v>596</v>
       </c>
       <c r="B461">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C461" s="1">
         <v>1171388.0900000001</v>
@@ -23729,10 +23712,10 @@
         <v>596</v>
       </c>
       <c r="B462">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C462" s="1">
-        <v>1171388.1000000001</v>
+        <v>1171388.0900000001</v>
       </c>
       <c r="F462" t="s">
         <v>636</v>
@@ -23740,19 +23723,16 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>132</v>
+        <v>596</v>
       </c>
       <c r="B463">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C463" s="1">
-        <v>1742316.75</v>
-      </c>
-      <c r="D463" s="1">
-        <v>1742316.75</v>
+        <v>1171388.1000000001</v>
       </c>
       <c r="F463" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23760,7 +23740,7 @@
         <v>132</v>
       </c>
       <c r="B464">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C464" s="1">
         <v>1742316.75</v>
@@ -23777,7 +23757,7 @@
         <v>132</v>
       </c>
       <c r="B465">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C465" s="1">
         <v>1742316.75</v>
@@ -23794,13 +23774,16 @@
         <v>132</v>
       </c>
       <c r="B466">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C466" s="1">
         <v>1742316.75</v>
       </c>
+      <c r="D466" s="1">
+        <v>1742316.75</v>
+      </c>
       <c r="F466" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23808,7 +23791,7 @@
         <v>132</v>
       </c>
       <c r="B467">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C467" s="1">
         <v>1742316.75</v>
@@ -23822,30 +23805,27 @@
         <v>132</v>
       </c>
       <c r="B468">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C468" s="1">
         <v>1742316.75</v>
       </c>
-      <c r="D468" s="1">
-        <v>1742316.75</v>
-      </c>
       <c r="F468" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>337</v>
+        <v>132</v>
       </c>
       <c r="B469">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C469" s="1">
-        <v>2154623.92</v>
+        <v>1742316.75</v>
       </c>
       <c r="D469" s="1">
-        <v>2154623.92</v>
+        <v>1742316.75</v>
       </c>
       <c r="F469" t="s">
         <v>635</v>
@@ -23856,13 +23836,16 @@
         <v>337</v>
       </c>
       <c r="B470">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C470" s="1">
         <v>2154623.92</v>
       </c>
+      <c r="D470" s="1">
+        <v>2154623.92</v>
+      </c>
       <c r="F470" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23870,10 +23853,10 @@
         <v>337</v>
       </c>
       <c r="B471">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C471" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.92</v>
       </c>
       <c r="F471" t="s">
         <v>636</v>
@@ -23881,13 +23864,13 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>599</v>
+        <v>337</v>
       </c>
       <c r="B472">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C472" s="1">
-        <v>227988.94</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F472" t="s">
         <v>636</v>
@@ -23898,10 +23881,10 @@
         <v>599</v>
       </c>
       <c r="B473">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C473" s="1">
-        <v>1443929.98</v>
+        <v>227988.94</v>
       </c>
       <c r="F473" t="s">
         <v>636</v>
@@ -23912,10 +23895,10 @@
         <v>599</v>
       </c>
       <c r="B474">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C474" s="1">
-        <v>1443929.97</v>
+        <v>1443929.98</v>
       </c>
       <c r="F474" t="s">
         <v>636</v>
@@ -23926,7 +23909,7 @@
         <v>599</v>
       </c>
       <c r="B475">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C475" s="1">
         <v>1443929.97</v>
@@ -23937,19 +23920,16 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>137</v>
+        <v>599</v>
       </c>
       <c r="B476">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C476" s="1">
-        <v>814633.04</v>
-      </c>
-      <c r="D476" s="1">
-        <v>814633.04</v>
+        <v>1443929.97</v>
       </c>
       <c r="F476" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23957,13 +23937,13 @@
         <v>137</v>
       </c>
       <c r="B477">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C477" s="1">
-        <v>814633.02</v>
+        <v>814633.04</v>
       </c>
       <c r="D477" s="1">
-        <v>814633.02</v>
+        <v>814633.04</v>
       </c>
       <c r="F477" t="s">
         <v>635</v>
@@ -23974,13 +23954,16 @@
         <v>137</v>
       </c>
       <c r="B478">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C478" s="1">
         <v>814633.02</v>
       </c>
+      <c r="D478" s="1">
+        <v>814633.02</v>
+      </c>
       <c r="F478" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23988,7 +23971,7 @@
         <v>137</v>
       </c>
       <c r="B479">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C479" s="1">
         <v>814633.02</v>
@@ -23999,19 +23982,16 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>342</v>
+        <v>137</v>
       </c>
       <c r="B480">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C480" s="1">
-        <v>1299174.74</v>
-      </c>
-      <c r="D480" s="1">
-        <v>1299174.74</v>
+        <v>814633.02</v>
       </c>
       <c r="F480" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -24019,13 +23999,13 @@
         <v>342</v>
       </c>
       <c r="B481">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C481" s="1">
-        <v>3247936.84</v>
+        <v>1299174.74</v>
       </c>
       <c r="D481" s="1">
-        <v>3247936.84</v>
+        <v>1299174.74</v>
       </c>
       <c r="F481" t="s">
         <v>635</v>
@@ -24036,13 +24016,13 @@
         <v>342</v>
       </c>
       <c r="B482">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C482" s="1">
-        <v>1948762.11</v>
+        <v>3247936.84</v>
       </c>
       <c r="D482" s="1">
-        <v>1948762.11</v>
+        <v>3247936.84</v>
       </c>
       <c r="F482" t="s">
         <v>635</v>
@@ -24050,16 +24030,19 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>602</v>
+        <v>342</v>
       </c>
       <c r="B483">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C483" s="1">
-        <v>247431.42</v>
+        <v>1948762.11</v>
+      </c>
+      <c r="D483" s="1">
+        <v>1948762.11</v>
       </c>
       <c r="F483" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -24067,10 +24050,10 @@
         <v>602</v>
       </c>
       <c r="B484">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C484" s="1">
-        <v>940239.41</v>
+        <v>247431.42</v>
       </c>
       <c r="F484" t="s">
         <v>636</v>
@@ -24081,7 +24064,7 @@
         <v>602</v>
       </c>
       <c r="B485">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C485" s="1">
         <v>940239.41</v>
@@ -24095,7 +24078,7 @@
         <v>602</v>
       </c>
       <c r="B486">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C486" s="1">
         <v>940239.41</v>
@@ -24109,7 +24092,7 @@
         <v>602</v>
       </c>
       <c r="B487">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C487" s="1">
         <v>940239.41</v>
@@ -24123,7 +24106,7 @@
         <v>602</v>
       </c>
       <c r="B488">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C488" s="1">
         <v>940239.41</v>
@@ -24134,13 +24117,13 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>140</v>
+        <v>602</v>
       </c>
       <c r="B489">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C489" s="1">
-        <v>735340.59</v>
+        <v>940239.41</v>
       </c>
       <c r="F489" t="s">
         <v>636</v>
@@ -24151,10 +24134,10 @@
         <v>140</v>
       </c>
       <c r="B490">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C490" s="1">
-        <v>735340.58</v>
+        <v>735340.59</v>
       </c>
       <c r="F490" t="s">
         <v>636</v>
@@ -24165,7 +24148,7 @@
         <v>140</v>
       </c>
       <c r="B491">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C491" s="1">
         <v>735340.58</v>
@@ -24179,7 +24162,7 @@
         <v>140</v>
       </c>
       <c r="B492">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C492" s="1">
         <v>735340.58</v>
@@ -24193,7 +24176,7 @@
         <v>140</v>
       </c>
       <c r="B493">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C493" s="1">
         <v>735340.58</v>
@@ -24207,7 +24190,7 @@
         <v>140</v>
       </c>
       <c r="B494">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C494" s="1">
         <v>735340.58</v>
@@ -24218,13 +24201,13 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>347</v>
+        <v>140</v>
       </c>
       <c r="B495">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C495" s="1">
-        <v>2165291.23</v>
+        <v>735340.58</v>
       </c>
       <c r="F495" t="s">
         <v>636</v>
@@ -24235,7 +24218,7 @@
         <v>347</v>
       </c>
       <c r="B496">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C496" s="1">
         <v>2165291.23</v>
@@ -24249,7 +24232,7 @@
         <v>347</v>
       </c>
       <c r="B497">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C497" s="1">
         <v>2165291.23</v>
@@ -24260,13 +24243,13 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>605</v>
+        <v>347</v>
       </c>
       <c r="B498">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C498" s="1">
-        <v>810252.48</v>
+        <v>2165291.23</v>
       </c>
       <c r="F498" t="s">
         <v>636</v>
@@ -24277,10 +24260,10 @@
         <v>605</v>
       </c>
       <c r="B499">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C499" s="1">
-        <v>1924349.63</v>
+        <v>810252.48</v>
       </c>
       <c r="F499" t="s">
         <v>636</v>
@@ -24291,7 +24274,7 @@
         <v>605</v>
       </c>
       <c r="B500">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C500" s="1">
         <v>1924349.63</v>
@@ -24305,7 +24288,7 @@
         <v>605</v>
       </c>
       <c r="B501">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C501" s="1">
         <v>1924349.63</v>
@@ -24319,7 +24302,7 @@
         <v>605</v>
       </c>
       <c r="B502">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C502" s="1">
         <v>1924349.63</v>
@@ -24333,7 +24316,7 @@
         <v>605</v>
       </c>
       <c r="B503">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C503" s="1">
         <v>1924349.63</v>
@@ -24347,7 +24330,7 @@
         <v>605</v>
       </c>
       <c r="B504">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C504" s="1">
         <v>1924349.63</v>
@@ -24361,7 +24344,7 @@
         <v>605</v>
       </c>
       <c r="B505">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C505" s="1">
         <v>1924349.63</v>
@@ -24375,10 +24358,10 @@
         <v>605</v>
       </c>
       <c r="B506">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C506" s="1">
-        <v>1924349.67</v>
+        <v>1924349.63</v>
       </c>
       <c r="F506" t="s">
         <v>636</v>
@@ -24386,19 +24369,16 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>145</v>
+        <v>605</v>
       </c>
       <c r="B507">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C507" s="1">
-        <v>1403662.7</v>
-      </c>
-      <c r="D507" s="1">
-        <v>1403662.7</v>
+        <v>1924349.67</v>
       </c>
       <c r="F507" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -24406,7 +24386,7 @@
         <v>145</v>
       </c>
       <c r="B508">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C508" s="1">
         <v>1403662.7</v>
@@ -24423,7 +24403,7 @@
         <v>145</v>
       </c>
       <c r="B509">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C509" s="1">
         <v>1403662.7</v>
@@ -24440,13 +24420,13 @@
         <v>145</v>
       </c>
       <c r="B510">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C510" s="1">
-        <v>1403662.71</v>
+        <v>1403662.7</v>
       </c>
       <c r="D510" s="1">
-        <v>1403662.71</v>
+        <v>1403662.7</v>
       </c>
       <c r="F510" t="s">
         <v>635</v>
@@ -24454,16 +24434,16 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>352</v>
+        <v>145</v>
       </c>
       <c r="B511">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C511" s="1">
-        <v>2165291.23</v>
+        <v>1403662.71</v>
       </c>
       <c r="D511" s="1">
-        <v>2165291.23</v>
+        <v>1403662.71</v>
       </c>
       <c r="F511" t="s">
         <v>635</v>
@@ -24474,7 +24454,7 @@
         <v>352</v>
       </c>
       <c r="B512">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C512" s="1">
         <v>2165291.23</v>
@@ -24491,30 +24471,30 @@
         <v>352</v>
       </c>
       <c r="B513">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C513" s="1">
         <v>2165291.23</v>
       </c>
+      <c r="D513" s="1">
+        <v>2165291.23</v>
+      </c>
       <c r="F513" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>150</v>
+        <v>352</v>
       </c>
       <c r="B514">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C514" s="1">
-        <v>800605.1</v>
-      </c>
-      <c r="D514" s="1">
-        <v>800605.1</v>
+        <v>2165291.23</v>
       </c>
       <c r="F514" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
@@ -24522,13 +24502,13 @@
         <v>150</v>
       </c>
       <c r="B515">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C515" s="1">
-        <v>800605.09</v>
+        <v>800605.1</v>
       </c>
       <c r="D515" s="1">
-        <v>800605.09</v>
+        <v>800605.1</v>
       </c>
       <c r="F515" t="s">
         <v>635</v>
@@ -24539,24 +24519,27 @@
         <v>150</v>
       </c>
       <c r="B516">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C516" s="1">
         <v>800605.09</v>
       </c>
+      <c r="D516" s="1">
+        <v>800605.09</v>
+      </c>
       <c r="F516" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>357</v>
+        <v>150</v>
       </c>
       <c r="B517">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C517" s="1">
-        <v>2154623.9300000002</v>
+        <v>800605.09</v>
       </c>
       <c r="F517" t="s">
         <v>636</v>
@@ -24567,10 +24550,10 @@
         <v>357</v>
       </c>
       <c r="B518">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C518" s="1">
-        <v>2154623.92</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F518" t="s">
         <v>636</v>
@@ -24581,7 +24564,7 @@
         <v>357</v>
       </c>
       <c r="B519">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C519" s="1">
         <v>2154623.92</v>
@@ -24592,19 +24575,16 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>155</v>
+        <v>357</v>
       </c>
       <c r="B520">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C520" s="1">
-        <v>1609832.04</v>
-      </c>
-      <c r="D520" s="1">
-        <v>1609832.04</v>
+        <v>2154623.92</v>
       </c>
       <c r="F520" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -24612,7 +24592,7 @@
         <v>155</v>
       </c>
       <c r="B521">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C521" s="1">
         <v>1609832.04</v>
@@ -24629,13 +24609,13 @@
         <v>155</v>
       </c>
       <c r="B522">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C522" s="1">
-        <v>1609832.03</v>
+        <v>1609832.04</v>
       </c>
       <c r="D522" s="1">
-        <v>1609832.03</v>
+        <v>1609832.04</v>
       </c>
       <c r="F522" t="s">
         <v>635</v>
@@ -24643,16 +24623,19 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>362</v>
+        <v>155</v>
       </c>
       <c r="B523">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C523" s="1">
-        <v>2154623.92</v>
+        <v>1609832.03</v>
+      </c>
+      <c r="D523" s="1">
+        <v>1609832.03</v>
       </c>
       <c r="F523" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -24660,7 +24643,7 @@
         <v>362</v>
       </c>
       <c r="B524">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C524" s="1">
         <v>2154623.92</v>
@@ -24674,10 +24657,10 @@
         <v>362</v>
       </c>
       <c r="B525">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C525" s="1">
-        <v>2154623.9300000002</v>
+        <v>2154623.92</v>
       </c>
       <c r="F525" t="s">
         <v>636</v>
@@ -24685,19 +24668,16 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="B526">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C526" s="1">
-        <v>657850.22</v>
-      </c>
-      <c r="D526" s="1">
-        <v>657850.22</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F526" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
@@ -24705,13 +24685,13 @@
         <v>160</v>
       </c>
       <c r="B527">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C527" s="1">
-        <v>657850.23</v>
+        <v>657850.22</v>
       </c>
       <c r="D527" s="1">
-        <v>657850.23</v>
+        <v>657850.22</v>
       </c>
       <c r="F527" t="s">
         <v>635</v>
@@ -24722,13 +24702,16 @@
         <v>160</v>
       </c>
       <c r="B528">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C528" s="1">
         <v>657850.23</v>
       </c>
+      <c r="D528" s="1">
+        <v>657850.23</v>
+      </c>
       <c r="F528" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
@@ -24736,30 +24719,27 @@
         <v>160</v>
       </c>
       <c r="B529">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C529" s="1">
         <v>657850.23</v>
       </c>
-      <c r="D529" s="1">
-        <v>657850.23</v>
-      </c>
       <c r="F529" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>367</v>
+        <v>160</v>
       </c>
       <c r="B530">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C530" s="1">
-        <v>2165291.23</v>
+        <v>657850.23</v>
       </c>
       <c r="D530" s="1">
-        <v>2165291.23</v>
+        <v>657850.23</v>
       </c>
       <c r="F530" t="s">
         <v>635</v>
@@ -24770,13 +24750,16 @@
         <v>367</v>
       </c>
       <c r="B531">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C531" s="1">
         <v>2165291.23</v>
       </c>
+      <c r="D531" s="1">
+        <v>2165291.23</v>
+      </c>
       <c r="F531" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
@@ -24784,7 +24767,7 @@
         <v>367</v>
       </c>
       <c r="B532">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C532" s="1">
         <v>2165291.23</v>
@@ -24795,13 +24778,13 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>163</v>
+        <v>367</v>
       </c>
       <c r="B533">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C533" s="1">
-        <v>718089.09</v>
+        <v>2165291.23</v>
       </c>
       <c r="F533" t="s">
         <v>636</v>
@@ -24812,7 +24795,7 @@
         <v>163</v>
       </c>
       <c r="B534">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C534" s="1">
         <v>718089.09</v>
@@ -24823,13 +24806,13 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>372</v>
+        <v>163</v>
       </c>
       <c r="B535">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C535" s="1">
-        <v>2154623.9300000002</v>
+        <v>718089.09</v>
       </c>
       <c r="F535" t="s">
         <v>636</v>
@@ -24840,7 +24823,7 @@
         <v>372</v>
       </c>
       <c r="B536">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C536" s="1">
         <v>2154623.9300000002</v>
@@ -24854,10 +24837,10 @@
         <v>372</v>
       </c>
       <c r="B537">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C537" s="1">
-        <v>2154623.92</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F537" t="s">
         <v>636</v>
@@ -24865,19 +24848,16 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B538">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C538" s="1">
-        <v>2109735.9300000002</v>
-      </c>
-      <c r="D538" s="1">
-        <v>2109735.9300000002</v>
+        <v>2154623.92</v>
       </c>
       <c r="F538" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
@@ -24885,13 +24865,16 @@
         <v>377</v>
       </c>
       <c r="B539">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C539" s="1">
         <v>2109735.9300000002</v>
       </c>
+      <c r="D539" s="1">
+        <v>2109735.9300000002</v>
+      </c>
       <c r="F539" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -24899,7 +24882,7 @@
         <v>377</v>
       </c>
       <c r="B540">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C540" s="1">
         <v>2109735.9300000002</v>
@@ -24910,19 +24893,16 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B541">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C541" s="1">
-        <v>2165291.23</v>
-      </c>
-      <c r="D541" s="1">
-        <v>2165291.23</v>
+        <v>2109735.9300000002</v>
       </c>
       <c r="F541" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
@@ -24930,13 +24910,16 @@
         <v>382</v>
       </c>
       <c r="B542">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C542" s="1">
         <v>2165291.23</v>
       </c>
+      <c r="D542" s="1">
+        <v>2165291.23</v>
+      </c>
       <c r="F542" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -24944,7 +24927,7 @@
         <v>382</v>
       </c>
       <c r="B543">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C543" s="1">
         <v>2165291.23</v>
@@ -24955,19 +24938,16 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B544">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C544" s="1">
-        <v>2154623.94</v>
-      </c>
-      <c r="D544" s="1">
-        <v>2154623.94</v>
+        <v>2165291.23</v>
       </c>
       <c r="F544" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -24975,13 +24955,13 @@
         <v>387</v>
       </c>
       <c r="B545">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C545" s="1">
-        <v>2154623.92</v>
+        <v>2154623.94</v>
       </c>
       <c r="D545" s="1">
-        <v>2154623.92</v>
+        <v>2154623.94</v>
       </c>
       <c r="F545" t="s">
         <v>635</v>
@@ -24992,24 +24972,27 @@
         <v>387</v>
       </c>
       <c r="B546">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C546" s="1">
         <v>2154623.92</v>
       </c>
+      <c r="D546" s="1">
+        <v>2154623.92</v>
+      </c>
       <c r="F546" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B547">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C547" s="1">
-        <v>2165291.23</v>
+        <v>2154623.92</v>
       </c>
       <c r="F547" t="s">
         <v>636</v>
@@ -25020,7 +25003,7 @@
         <v>390</v>
       </c>
       <c r="B548">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C548" s="1">
         <v>2165291.23</v>
@@ -25034,7 +25017,7 @@
         <v>390</v>
       </c>
       <c r="B549">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C549" s="1">
         <v>2165291.23</v>
@@ -25045,13 +25028,13 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B550">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C550" s="1">
-        <v>2132179.9300000002</v>
+        <v>2165291.23</v>
       </c>
       <c r="F550" t="s">
         <v>636</v>
@@ -25062,7 +25045,7 @@
         <v>395</v>
       </c>
       <c r="B551">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C551" s="1">
         <v>2132179.9300000002</v>
@@ -25076,7 +25059,7 @@
         <v>395</v>
       </c>
       <c r="B552">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C552" s="1">
         <v>2132179.9300000002</v>
@@ -25087,10 +25070,10 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B553">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C553" s="1">
         <v>2132179.9300000002</v>
@@ -25104,7 +25087,7 @@
         <v>398</v>
       </c>
       <c r="B554">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C554" s="1">
         <v>2132179.9300000002</v>
@@ -25118,7 +25101,7 @@
         <v>398</v>
       </c>
       <c r="B555">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C555" s="1">
         <v>2132179.9300000002</v>
@@ -25129,19 +25112,16 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B556">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C556" s="1">
-        <v>2154623.9300000002</v>
-      </c>
-      <c r="D556" s="1">
-        <v>2154623.9300000002</v>
+        <v>2132179.9300000002</v>
       </c>
       <c r="F556" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
@@ -25149,13 +25129,13 @@
         <v>403</v>
       </c>
       <c r="B557">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C557" s="1">
-        <v>2154623.92</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="D557" s="1">
-        <v>2154623.92</v>
+        <v>2154623.9300000002</v>
       </c>
       <c r="F557" t="s">
         <v>635</v>
@@ -25166,7 +25146,7 @@
         <v>403</v>
       </c>
       <c r="B558">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C558" s="1">
         <v>2154623.92</v>
@@ -25180,16 +25160,19 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B559">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C559" s="1">
-        <v>2109735.9300000002</v>
+        <v>2154623.92</v>
+      </c>
+      <c r="D559" s="1">
+        <v>2154623.92</v>
       </c>
       <c r="F559" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -25197,7 +25180,7 @@
         <v>406</v>
       </c>
       <c r="B560">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C560" s="1">
         <v>2109735.9300000002</v>
@@ -25211,7 +25194,7 @@
         <v>406</v>
       </c>
       <c r="B561">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C561" s="1">
         <v>2109735.9300000002</v>
@@ -25222,19 +25205,16 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
+        <v>406</v>
+      </c>
+      <c r="B562">
         <v>3</v>
       </c>
-      <c r="B562">
-        <v>1</v>
-      </c>
       <c r="C562" s="1">
-        <v>426344.15</v>
-      </c>
-      <c r="D562" s="1">
-        <v>426344.15</v>
+        <v>2109735.9300000002</v>
       </c>
       <c r="F562" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
@@ -25242,7 +25222,7 @@
         <v>3</v>
       </c>
       <c r="B563">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C563" s="1">
         <v>426344.15</v>
@@ -25259,7 +25239,7 @@
         <v>3</v>
       </c>
       <c r="B564">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C564" s="1">
         <v>426344.15</v>
@@ -25276,7 +25256,7 @@
         <v>3</v>
       </c>
       <c r="B565">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C565" s="1">
         <v>426344.15</v>
@@ -25293,7 +25273,7 @@
         <v>3</v>
       </c>
       <c r="B566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C566" s="1">
         <v>426344.15</v>
@@ -25310,7 +25290,7 @@
         <v>3</v>
       </c>
       <c r="B567">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C567" s="1">
         <v>426344.15</v>
@@ -25324,16 +25304,16 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B568">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C568" s="1">
-        <v>386235</v>
+        <v>426344.15</v>
       </c>
       <c r="D568" s="1">
-        <v>386235</v>
+        <v>426344.15</v>
       </c>
       <c r="F568" t="s">
         <v>635</v>
@@ -25344,13 +25324,13 @@
         <v>9</v>
       </c>
       <c r="B569">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C569" s="1">
-        <v>491542.26</v>
+        <v>386235</v>
       </c>
       <c r="D569" s="1">
-        <v>491542.26</v>
+        <v>386235</v>
       </c>
       <c r="F569" t="s">
         <v>635</v>
@@ -25361,13 +25341,13 @@
         <v>9</v>
       </c>
       <c r="B570">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C570" s="1">
-        <v>491542.27</v>
+        <v>491542.26</v>
       </c>
       <c r="D570" s="1">
-        <v>491542.27</v>
+        <v>491542.26</v>
       </c>
       <c r="F570" t="s">
         <v>635</v>
@@ -25378,7 +25358,7 @@
         <v>9</v>
       </c>
       <c r="B571">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C571" s="1">
         <v>491542.27</v>
@@ -25395,13 +25375,16 @@
         <v>9</v>
       </c>
       <c r="B572">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C572" s="1">
         <v>491542.27</v>
       </c>
+      <c r="D572" s="1">
+        <v>491542.27</v>
+      </c>
       <c r="F572" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
@@ -25409,7 +25392,7 @@
         <v>9</v>
       </c>
       <c r="B573">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C573" s="1">
         <v>491542.27</v>
@@ -25423,7 +25406,7 @@
         <v>9</v>
       </c>
       <c r="B574">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C574" s="1">
         <v>491542.27</v>
@@ -25434,19 +25417,16 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B575">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C575" s="1">
-        <v>148660.32</v>
-      </c>
-      <c r="D575" s="1">
-        <v>148660.32</v>
+        <v>491542.27</v>
       </c>
       <c r="F575" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -25454,13 +25434,13 @@
         <v>14</v>
       </c>
       <c r="B576">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C576" s="1">
-        <v>489749.93</v>
+        <v>148660.32</v>
       </c>
       <c r="D576" s="1">
-        <v>489749.93</v>
+        <v>148660.32</v>
       </c>
       <c r="F576" t="s">
         <v>635</v>
@@ -25471,7 +25451,7 @@
         <v>14</v>
       </c>
       <c r="B577">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C577" s="1">
         <v>489749.93</v>
@@ -25488,7 +25468,7 @@
         <v>14</v>
       </c>
       <c r="B578">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C578" s="1">
         <v>489749.93</v>
@@ -25505,7 +25485,7 @@
         <v>14</v>
       </c>
       <c r="B579">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C579" s="1">
         <v>489749.93</v>
@@ -25522,7 +25502,7 @@
         <v>14</v>
       </c>
       <c r="B580">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C580" s="1">
         <v>489749.93</v>
@@ -25539,13 +25519,13 @@
         <v>14</v>
       </c>
       <c r="B581">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C581" s="1">
-        <v>428044.92</v>
+        <v>489749.93</v>
       </c>
       <c r="D581" s="1">
-        <v>428044.92</v>
+        <v>489749.93</v>
       </c>
       <c r="F581" t="s">
         <v>635</v>
@@ -25556,7 +25536,7 @@
         <v>14</v>
       </c>
       <c r="B582">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C582" s="1">
         <v>428044.92</v>
@@ -25566,6 +25546,93 @@
       </c>
       <c r="F582" t="s">
         <v>635</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>14</v>
+      </c>
+      <c r="B583">
+        <v>8</v>
+      </c>
+      <c r="C583" s="1">
+        <v>428044.92</v>
+      </c>
+      <c r="D583" s="1">
+        <v>428044.92</v>
+      </c>
+      <c r="F583" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>557</v>
+      </c>
+      <c r="B584">
+        <v>1</v>
+      </c>
+      <c r="C584" s="1">
+        <v>127875.6</v>
+      </c>
+      <c r="F584" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>557</v>
+      </c>
+      <c r="B585">
+        <v>2</v>
+      </c>
+      <c r="C585" s="1">
+        <v>607409.07999999996</v>
+      </c>
+      <c r="F585" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>557</v>
+      </c>
+      <c r="B586">
+        <v>3</v>
+      </c>
+      <c r="C586" s="1">
+        <v>607409.07999999996</v>
+      </c>
+      <c r="F586" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>557</v>
+      </c>
+      <c r="B587">
+        <v>4</v>
+      </c>
+      <c r="C587" s="1">
+        <v>607409.07999999996</v>
+      </c>
+      <c r="F587" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>557</v>
+      </c>
+      <c r="B588">
+        <v>5</v>
+      </c>
+      <c r="C588" s="1">
+        <v>607409.07999999996</v>
+      </c>
+      <c r="F588" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -25661,8 +25728,8 @@
       <c r="A10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
-        <v>478</v>
+      <c r="B10" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -25931,122 +25998,122 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" t="s">
         <v>200</v>
-      </c>
-      <c r="B44" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>204</v>
+      </c>
+      <c r="B45" t="s">
         <v>205</v>
-      </c>
-      <c r="B45" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s">
         <v>210</v>
-      </c>
-      <c r="B46" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" t="s">
         <v>215</v>
-      </c>
-      <c r="B47" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" t="s">
         <v>219</v>
-      </c>
-      <c r="B48" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>223</v>
+      </c>
+      <c r="B49" t="s">
         <v>224</v>
-      </c>
-      <c r="B49" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>226</v>
+      </c>
+      <c r="B50" t="s">
         <v>227</v>
-      </c>
-      <c r="B50" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" t="s">
         <v>232</v>
-      </c>
-      <c r="B51" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" t="s">
         <v>237</v>
-      </c>
-      <c r="B52" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>239</v>
+      </c>
+      <c r="B53" t="s">
         <v>240</v>
-      </c>
-      <c r="B53" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>244</v>
+      </c>
+      <c r="B54" t="s">
         <v>245</v>
-      </c>
-      <c r="B54" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>249</v>
+      </c>
+      <c r="B55" t="s">
         <v>250</v>
-      </c>
-      <c r="B55" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>254</v>
+      </c>
+      <c r="B56" t="s">
         <v>255</v>
-      </c>
-      <c r="B56" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>258</v>
+      </c>
+      <c r="B57" t="s">
         <v>259</v>
-      </c>
-      <c r="B57" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>261</v>
+      </c>
+      <c r="B58" t="s">
         <v>262</v>
-      </c>
-      <c r="B58" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
